--- a/src/data/INSUMOS_BASICOS_AUTO.xlsx
+++ b/src/data/INSUMOS_BASICOS_AUTO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-I\EXCELS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\WebstormProjects\erpperu2-automation\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C98ADCB-A123-4424-90FE-1108621B3BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38EB0FC-5D7D-482E-BF4B-F7B2B68E190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31590" yWindow="2790" windowWidth="24000" windowHeight="10845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2796" yWindow="0" windowWidth="10620" windowHeight="12384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSUMOS" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>TIPO AFECTACION IGV</t>
   </si>
   <si>
-    <t>DESCRIPCION</t>
-  </si>
-  <si>
     <t>SI</t>
   </si>
   <si>
@@ -390,6 +387,9 @@
   </si>
   <si>
     <t>nuevo insumo flexible</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
   </si>
 </sst>
 </file>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -1022,28 +1022,28 @@
         <v>444444</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
         <v>114</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1051,28 +1051,28 @@
         <v>464646</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1080,28 +1080,28 @@
         <v>444666</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1109,28 +1109,28 @@
         <v>666444</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2521,551 +2521,551 @@
     <row r="1" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="55" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="119" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B121" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B122" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/INSUMOS_BASICOS_AUTO.xlsx
+++ b/src/data/INSUMOS_BASICOS_AUTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\WebstormProjects\erpperu2-automation\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38EB0FC-5D7D-482E-BF4B-F7B2B68E190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1E79AF-3409-41E8-9341-B1AA4E77AB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2796" yWindow="0" windowWidth="10620" windowHeight="12384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31065" yWindow="2265" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSUMOS" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="122">
   <si>
     <t xml:space="preserve">CODIGO </t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>STOCK</t>
   </si>
 </sst>
 </file>
@@ -976,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
@@ -988,7 +991,7 @@
     <col min="9" max="9" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1016,8 +1019,11 @@
       <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>444444</v>
       </c>
@@ -1046,7 +1052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16">
         <v>464646</v>
       </c>
@@ -1075,7 +1081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16">
         <v>444666</v>
       </c>
@@ -1101,10 +1107,13 @@
         <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
         <v>666444</v>
       </c>
@@ -1133,13 +1142,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
@@ -1150,7 +1159,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
@@ -1161,7 +1170,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10"/>
@@ -1172,7 +1181,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
@@ -1183,7 +1192,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
@@ -1194,7 +1203,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
@@ -1205,7 +1214,7 @@
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
@@ -1216,7 +1225,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="10"/>
@@ -1227,7 +1236,7 @@
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
@@ -1238,7 +1247,7 @@
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="7" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
